--- a/results/phase1/ViT_26/0_F1_VIT.xlsx
+++ b/results/phase1/ViT_26/0_F1_VIT.xlsx
@@ -487,7 +487,7 @@
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
   <dimension ref="A1:B12"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="11.640625" defaultRowHeight="12.75" zeroHeight="0" outlineLevelRow="0"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="11.66015625" defaultRowHeight="12.75" zeroHeight="0" outlineLevelRow="0"/>
   <sheetData>
     <row r="1" ht="13.5" customHeight="1" s="8">
       <c r="A1" s="9" t="inlineStr">
@@ -592,7 +592,7 @@
         </is>
       </c>
       <c r="B10" s="9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" ht="23.25" customHeight="1" s="8">
@@ -602,7 +602,7 @@
         </is>
       </c>
       <c r="B11" s="9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12" ht="13.5" customHeight="1" s="8">
@@ -637,7 +637,7 @@
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
   <dimension ref="A1:I433"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.625" defaultRowHeight="13.5" zeroHeight="0" outlineLevelRow="0"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.640625" defaultRowHeight="13.5" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="13.37" customWidth="1" style="9" min="2" max="2"/>
     <col width="14.03" customWidth="1" style="9" min="3" max="3"/>
@@ -2481,8 +2481,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:Q9"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="11.60546875" defaultRowHeight="12.75" zeroHeight="0" outlineLevelRow="0"/>
+  <dimension ref="A1:Q12"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="11.625" defaultRowHeight="12.75" zeroHeight="0" outlineLevelRow="0"/>
   <sheetData>
     <row r="1" ht="15" customHeight="1" s="8">
       <c r="A1" s="9" t="inlineStr">
@@ -2918,58 +2918,229 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="n">
+    <row r="9" ht="12.75" customHeight="1" s="8">
+      <c r="A9" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="9" t="inlineStr">
         <is>
           <t>VIT_B16</t>
         </is>
       </c>
-      <c r="C9" t="n">
+      <c r="C9" s="9" t="n">
         <v>7</v>
       </c>
-      <c r="D9" t="n">
-        <v>1.212227702140808</v>
-      </c>
-      <c r="E9" t="n">
+      <c r="D9" s="9" t="n">
+        <v>1.21222770214081</v>
+      </c>
+      <c r="E9" s="9" t="n">
         <v>0.968</v>
       </c>
-      <c r="F9" t="n">
-        <v>1.180042386054993</v>
-      </c>
-      <c r="G9" t="n">
+      <c r="F9" s="9" t="n">
+        <v>1.18004238605499</v>
+      </c>
+      <c r="G9" s="9" t="n">
         <v>0.974</v>
       </c>
-      <c r="H9" t="n">
+      <c r="H9" s="9" t="n">
         <v>0.976</v>
       </c>
-      <c r="I9" t="n">
+      <c r="I9" s="9" t="n">
         <v>0.974</v>
       </c>
-      <c r="J9" t="n">
+      <c r="J9" s="9" t="n">
         <v>0.973</v>
       </c>
-      <c r="K9" t="n">
+      <c r="K9" s="9" t="n">
         <v>0.971</v>
       </c>
-      <c r="L9" s="14" t="n">
+      <c r="L9" s="12" t="n">
         <v>46048.34425925926</v>
       </c>
-      <c r="M9" s="14" t="n">
+      <c r="M9" s="12" t="n">
         <v>46048.38412037037</v>
       </c>
-      <c r="N9" s="15" t="n">
+      <c r="N9" s="13" t="n">
         <v>0.03986111111111111</v>
       </c>
-      <c r="O9" t="n">
+      <c r="O9" s="9" t="n">
         <v>14</v>
       </c>
-      <c r="P9" t="n">
+      <c r="P9" s="9" t="n">
         <v>24</v>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="Q9" s="9" t="inlineStr">
+        <is>
+          <t>VIT_K10_xlsx_26.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>VIT_B16</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="D10" s="9" t="n">
+        <v>1.19617486000061</v>
+      </c>
+      <c r="E10" s="9" t="n">
+        <v>0.968</v>
+      </c>
+      <c r="F10" s="9" t="n">
+        <v>1.156090378761292</v>
+      </c>
+      <c r="G10" s="9" t="n">
+        <v>0.986</v>
+      </c>
+      <c r="H10" s="9" t="n">
+        <v>0.987</v>
+      </c>
+      <c r="I10" s="9" t="n">
+        <v>0.986</v>
+      </c>
+      <c r="J10" s="9" t="n">
+        <v>0.986</v>
+      </c>
+      <c r="K10" s="9" t="n">
+        <v>0.984</v>
+      </c>
+      <c r="L10" s="14" t="n">
+        <v>46049.656875</v>
+      </c>
+      <c r="M10" s="14" t="n">
+        <v>46049.69832175926</v>
+      </c>
+      <c r="N10" s="15" t="n">
+        <v>0.04144675925925926</v>
+      </c>
+      <c r="O10" s="9" t="n">
+        <v>15</v>
+      </c>
+      <c r="P10" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="Q10" s="9" t="inlineStr">
+        <is>
+          <t>VIT_K10_xlsx_26.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>VIT_B16</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="n">
+        <v>9</v>
+      </c>
+      <c r="D11" s="9" t="n">
+        <v>1.183658599853516</v>
+      </c>
+      <c r="E11" s="9" t="n">
+        <v>0.977</v>
+      </c>
+      <c r="F11" s="9" t="n">
+        <v>1.11891233921051</v>
+      </c>
+      <c r="G11" s="9" t="n">
+        <v>0.993</v>
+      </c>
+      <c r="H11" s="9" t="n">
+        <v>0.993</v>
+      </c>
+      <c r="I11" s="9" t="n">
+        <v>0.993</v>
+      </c>
+      <c r="J11" s="9" t="n">
+        <v>0.993</v>
+      </c>
+      <c r="K11" s="9" t="n">
+        <v>0.992</v>
+      </c>
+      <c r="L11" s="14" t="n">
+        <v>46049.69863425926</v>
+      </c>
+      <c r="M11" s="14" t="n">
+        <v>46049.7615162037</v>
+      </c>
+      <c r="N11" s="15" t="n">
+        <v>0.06288194444444445</v>
+      </c>
+      <c r="O11" s="9" t="n">
+        <v>28</v>
+      </c>
+      <c r="P11" s="9" t="n">
+        <v>38</v>
+      </c>
+      <c r="Q11" s="9" t="inlineStr">
+        <is>
+          <t>VIT_K10_xlsx_26.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>0</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>VIT_B16</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>10</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1.195788383483887</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.974</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1.19706916809082</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.974</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.974</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.974</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.973</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.971</v>
+      </c>
+      <c r="L12" s="14" t="n">
+        <v>46049.7618287037</v>
+      </c>
+      <c r="M12" s="14" t="n">
+        <v>46049.8065625</v>
+      </c>
+      <c r="N12" s="15" t="n">
+        <v>0.0447337962962963</v>
+      </c>
+      <c r="O12" t="n">
+        <v>17</v>
+      </c>
+      <c r="P12" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q12" t="inlineStr">
         <is>
           <t>VIT_K10_xlsx_26.py</t>
         </is>
